--- a/data/samples/dirty/promotion_plan.xlsx
+++ b/data/samples/dirty/promotion_plan.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,17 +474,14 @@
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>7000</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>discount</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>buy 2</t>
         </is>
       </c>
     </row>
@@ -509,8 +506,10 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>12000</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -544,8 +543,10 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>2000</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -579,8 +580,10 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>5000</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -588,6 +591,117 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>buy 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P-5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SKU-4</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>buy 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P-6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SKU-5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>buy 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P-7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SKU-6</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>buy 1</t>
         </is>
